--- a/outputs/faq-chatbot/FAQ_Chatbot_Data.xlsx
+++ b/outputs/faq-chatbot/FAQ_Chatbot_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frcmongolia-my.sharepoint.com/personal/delgermaa_frc_mn/Documents/Documents/GitHub/frc_frontend/outputs/faq-chatbot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_CD600E785A1BBF5C12BC81CD29DD7CE5B966D982" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94DF5834-3B5D-4FC5-8F02-DF264312BFDD}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_CD600E785A1BBF5C12BC81CD29DD7CE5B966D982" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5595F1DA-973B-45C1-8F86-1236D433883B}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="415">
   <si>
     <t>№</t>
   </si>
@@ -897,39 +897,6 @@
     <t>Залилан, луйвар зэрэг гэмт хэрэгтэй холбоотой мэдээллийг хууль сахиулах байгууллагад мэдээлэх нь зүйтэй. СЗХ-ны зохицуулалттай этгээдийн хувьд хууль сахиулах байгууллагад мэдээлэхээс гадна СМА-ны goAML системд сэжигтэй гүйлгээний тайлангаар мэдээллийг илгээх хэрэгтэй.</t>
   </si>
   <si>
-    <t>faq-018</t>
-  </si>
-  <si>
-    <t>faq-019</t>
-  </si>
-  <si>
-    <t>faq-020</t>
-  </si>
-  <si>
-    <t>faq-021</t>
-  </si>
-  <si>
-    <t>faq-022</t>
-  </si>
-  <si>
-    <t>faq-023</t>
-  </si>
-  <si>
-    <t>faq-024</t>
-  </si>
-  <si>
-    <t>faq-025</t>
-  </si>
-  <si>
-    <t>faq-026</t>
-  </si>
-  <si>
-    <t>faq-027</t>
-  </si>
-  <si>
-    <t>faq-028</t>
-  </si>
-  <si>
     <t>faq-029</t>
   </si>
   <si>
@@ -1364,6 +1331,30 @@
   </si>
   <si>
     <t>Салбаруудын холбоо барих мэдээлэл</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Банк бус санхүүгийн байгууллага, Хадгаламж зээлийн хоршоо, Үнэт цаас, Даатгал, Үнэт металл үнэт эдлэл, Үл хөдлөх эд хөрөнгө зуучлал, Виртуал хөрөнгийн үйлчилгээ үзүүлэгч, Мөнгөн зээлийн үйл ажиллагаа эрхлэгч, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Үнэт цаас </t>
+  </si>
+  <si>
+    <t>Үнэт цаас</t>
+  </si>
+  <si>
+    <t>Банк бус санхүүгийн байгууллага</t>
+  </si>
+  <si>
+    <t>Цаасан  болон цахим хэлбэрээр ирүүлнэ. Цахимаар бол "info@frc.mn" мэйл хаяганд, цаасан хэлбэрээр СЗХ-ны 102 тоотод, Өргөдөл, гомдолын асуудал-51-261275</t>
+  </si>
+  <si>
+    <t>Цаасан  болон цахим хэлбэрээр ирүүлнэ. Цахимаар бол "info@frc.mn" мэйл хаяганд, цаасан хэлбэрээр СЗХ-ны 102 тоотод. Өргөдөл, гомдолын асуудал-51-261275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мөнгөн зээлийн үйл ажиллагаа эрхлэгч </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Даатгал </t>
   </si>
 </sst>
 </file>
@@ -1955,8 +1946,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FaqDataTable" displayName="FaqDataTable" ref="A1:M118" totalsRowShown="0">
-  <autoFilter ref="A1:M118" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FaqDataTable" displayName="FaqDataTable" ref="A1:M107" totalsRowShown="0">
+  <autoFilter ref="A1:M107" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="faq_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category"/>
@@ -3598,7 +3589,7 @@
   <sheetPr>
     <tabColor rgb="FF2957A4"/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3665,7 +3656,7 @@
         <v>239</v>
       </c>
       <c r="C2" s="60" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="D2" s="60" t="s">
         <v>4</v>
@@ -3725,7 +3716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A4" s="61" t="s">
         <v>246</v>
       </c>
@@ -3735,7 +3726,9 @@
       <c r="C4" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="60"/>
+      <c r="D4" s="60" t="s">
+        <v>407</v>
+      </c>
       <c r="E4" s="60"/>
       <c r="F4" s="60"/>
       <c r="G4" s="60"/>
@@ -3763,7 +3756,7 @@
         <v>249</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>239</v>
+        <v>408</v>
       </c>
       <c r="C5" s="60" t="s">
         <v>8</v>
@@ -3796,7 +3789,7 @@
         <v>251</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>239</v>
+        <v>409</v>
       </c>
       <c r="C6" s="60" t="s">
         <v>10</v>
@@ -3829,13 +3822,13 @@
         <v>253</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>239</v>
+        <v>410</v>
       </c>
       <c r="C7" s="60" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="60" t="s">
-        <v>6</v>
+        <v>411</v>
       </c>
       <c r="E7" s="60"/>
       <c r="F7" s="60"/>
@@ -3857,17 +3850,19 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A8" s="61" t="s">
         <v>254</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>239</v>
+        <v>410</v>
       </c>
       <c r="C8" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="60"/>
+      <c r="D8" s="60" t="s">
+        <v>412</v>
+      </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
       <c r="G8" s="60"/>
@@ -3895,7 +3890,7 @@
         <v>255</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>239</v>
+        <v>410</v>
       </c>
       <c r="C9" s="60" t="s">
         <v>14</v>
@@ -3961,7 +3956,7 @@
         <v>257</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>239</v>
+        <v>410</v>
       </c>
       <c r="C11" s="60" t="s">
         <v>18</v>
@@ -3994,7 +3989,7 @@
         <v>258</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>239</v>
+        <v>413</v>
       </c>
       <c r="C12" s="60" t="s">
         <v>20</v>
@@ -4027,7 +4022,7 @@
         <v>259</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>239</v>
+        <v>413</v>
       </c>
       <c r="C13" s="60" t="s">
         <v>22</v>
@@ -4062,7 +4057,7 @@
         <v>261</v>
       </c>
       <c r="B14" s="60" t="s">
-        <v>239</v>
+        <v>414</v>
       </c>
       <c r="C14" s="60" t="s">
         <v>24</v>
@@ -4095,7 +4090,7 @@
         <v>262</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>239</v>
+        <v>414</v>
       </c>
       <c r="C15" s="60" t="s">
         <v>26</v>
@@ -4128,7 +4123,7 @@
         <v>263</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>239</v>
+        <v>414</v>
       </c>
       <c r="C16" s="60" t="s">
         <v>28</v>
@@ -4161,7 +4156,7 @@
         <v>264</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>239</v>
+        <v>160</v>
       </c>
       <c r="C17" s="60" t="s">
         <v>30</v>
@@ -4222,17 +4217,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="61" t="s">
         <v>268</v>
       </c>
       <c r="B19" s="60" t="s">
-        <v>239</v>
+        <v>46</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="60"/>
+        <v>47</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>48</v>
+      </c>
       <c r="E19" s="60"/>
       <c r="F19" s="60"/>
       <c r="G19" s="60"/>
@@ -4240,32 +4237,30 @@
         <v>240</v>
       </c>
       <c r="I19" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J19" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J19" s="62"/>
       <c r="K19" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L19" s="60">
-        <v>19</v>
-      </c>
-      <c r="M19" s="60">
-        <v>18</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="M19" s="60"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="61" t="s">
         <v>269</v>
       </c>
       <c r="B20" s="60" t="s">
-        <v>239</v>
+        <v>46</v>
       </c>
       <c r="C20" s="60" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="60"/>
+        <v>49</v>
+      </c>
+      <c r="D20" s="60" t="s">
+        <v>50</v>
+      </c>
       <c r="E20" s="60"/>
       <c r="F20" s="60"/>
       <c r="G20" s="60"/>
@@ -4273,32 +4268,30 @@
         <v>240</v>
       </c>
       <c r="I20" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J20" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J20" s="62"/>
       <c r="K20" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L20" s="60">
-        <v>20</v>
-      </c>
-      <c r="M20" s="60">
-        <v>19</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="M20" s="60"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="61" t="s">
         <v>270</v>
       </c>
       <c r="B21" s="60" t="s">
-        <v>239</v>
+        <v>46</v>
       </c>
       <c r="C21" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="60"/>
+        <v>271</v>
+      </c>
+      <c r="D21" s="60" t="s">
+        <v>272</v>
+      </c>
       <c r="E21" s="60"/>
       <c r="F21" s="60"/>
       <c r="G21" s="60"/>
@@ -4306,32 +4299,30 @@
         <v>240</v>
       </c>
       <c r="I21" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J21" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J21" s="62"/>
       <c r="K21" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L21" s="60">
-        <v>21</v>
-      </c>
-      <c r="M21" s="60">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="M21" s="60"/>
+    </row>
+    <row r="22" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A22" s="61" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B22" s="60" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="60"/>
+        <v>53</v>
+      </c>
+      <c r="D22" s="60" t="s">
+        <v>54</v>
+      </c>
       <c r="E22" s="60"/>
       <c r="F22" s="60"/>
       <c r="G22" s="60"/>
@@ -4339,30 +4330,30 @@
         <v>240</v>
       </c>
       <c r="I22" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J22" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J22" s="62"/>
       <c r="K22" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L22" s="60">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="M22" s="60"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A23" s="61" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B23" s="60" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="60"/>
+        <v>56</v>
+      </c>
+      <c r="D23" s="60" t="s">
+        <v>275</v>
+      </c>
       <c r="E23" s="60"/>
       <c r="F23" s="60"/>
       <c r="G23" s="60"/>
@@ -4370,30 +4361,30 @@
         <v>240</v>
       </c>
       <c r="I23" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J23" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J23" s="62"/>
       <c r="K23" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L23" s="60">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="M23" s="60"/>
     </row>
-    <row r="24" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A24" s="61" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B24" s="60" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="60"/>
+        <v>58</v>
+      </c>
+      <c r="D24" s="60" t="s">
+        <v>59</v>
+      </c>
       <c r="E24" s="60"/>
       <c r="F24" s="60"/>
       <c r="G24" s="60"/>
@@ -4401,30 +4392,30 @@
         <v>240</v>
       </c>
       <c r="I24" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J24" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J24" s="62"/>
       <c r="K24" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L24" s="60">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="M24" s="60"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A25" s="61" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B25" s="60" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="60"/>
+        <v>60</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="E25" s="60"/>
       <c r="F25" s="60"/>
       <c r="G25" s="60"/>
@@ -4432,30 +4423,30 @@
         <v>240</v>
       </c>
       <c r="I25" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J25" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J25" s="62"/>
       <c r="K25" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L25" s="60">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="M25" s="60"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="216" x14ac:dyDescent="0.25">
       <c r="A26" s="61" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B26" s="60" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="60"/>
+        <v>62</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>280</v>
+      </c>
       <c r="E26" s="60"/>
       <c r="F26" s="60"/>
       <c r="G26" s="60"/>
@@ -4463,30 +4454,30 @@
         <v>240</v>
       </c>
       <c r="I26" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J26" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J26" s="62"/>
       <c r="K26" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L26" s="60">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="M26" s="60"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A27" s="61" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B27" s="60" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="60"/>
+        <v>64</v>
+      </c>
+      <c r="D27" s="60" t="s">
+        <v>65</v>
+      </c>
       <c r="E27" s="60"/>
       <c r="F27" s="60"/>
       <c r="G27" s="60"/>
@@ -4494,30 +4485,30 @@
         <v>240</v>
       </c>
       <c r="I27" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J27" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J27" s="62"/>
       <c r="K27" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L27" s="60">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M27" s="60"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A28" s="61" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B28" s="60" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="60"/>
+        <v>66</v>
+      </c>
+      <c r="D28" s="60" t="s">
+        <v>283</v>
+      </c>
       <c r="E28" s="60"/>
       <c r="F28" s="60"/>
       <c r="G28" s="60"/>
@@ -4525,30 +4516,30 @@
         <v>240</v>
       </c>
       <c r="I28" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J28" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J28" s="62"/>
       <c r="K28" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L28" s="60">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="M28" s="60"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="108" x14ac:dyDescent="0.25">
       <c r="A29" s="61" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B29" s="60" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="60"/>
+        <v>68</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>285</v>
+      </c>
       <c r="E29" s="60"/>
       <c r="F29" s="60"/>
       <c r="G29" s="60"/>
@@ -4556,31 +4547,29 @@
         <v>240</v>
       </c>
       <c r="I29" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J29" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J29" s="62"/>
       <c r="K29" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L29" s="60">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="M29" s="60"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A30" s="61" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B30" s="60" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D30" s="60" t="s">
-        <v>48</v>
+        <v>287</v>
       </c>
       <c r="E30" s="60"/>
       <c r="F30" s="60"/>
@@ -4596,22 +4585,22 @@
         <v>243</v>
       </c>
       <c r="L30" s="60">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="M30" s="60"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A31" s="61" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B31" s="60" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C31" s="60" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D31" s="60" t="s">
-        <v>50</v>
+        <v>289</v>
       </c>
       <c r="E31" s="60"/>
       <c r="F31" s="60"/>
@@ -4627,22 +4616,22 @@
         <v>243</v>
       </c>
       <c r="L31" s="60">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M31" s="60"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A32" s="61" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B32" s="60" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>282</v>
+        <v>74</v>
       </c>
       <c r="D32" s="60" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E32" s="60"/>
       <c r="F32" s="60"/>
@@ -4658,22 +4647,22 @@
         <v>243</v>
       </c>
       <c r="L32" s="60">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M32" s="60"/>
     </row>
-    <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A33" s="61" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C33" s="60" t="s">
-        <v>53</v>
+        <v>293</v>
       </c>
       <c r="D33" s="60" t="s">
-        <v>54</v>
+        <v>294</v>
       </c>
       <c r="E33" s="60"/>
       <c r="F33" s="60"/>
@@ -4689,22 +4678,24 @@
         <v>243</v>
       </c>
       <c r="L33" s="60">
-        <v>41</v>
-      </c>
-      <c r="M33" s="60"/>
+        <v>60</v>
+      </c>
+      <c r="M33" s="60">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A34" s="61" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B34" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="D34" s="60" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E34" s="60"/>
       <c r="F34" s="60"/>
@@ -4720,22 +4711,24 @@
         <v>243</v>
       </c>
       <c r="L34" s="60">
-        <v>46</v>
-      </c>
-      <c r="M34" s="60"/>
+        <v>61</v>
+      </c>
+      <c r="M34" s="60">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A35" s="61" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B35" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C35" s="60" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="D35" s="60" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="E35" s="60"/>
       <c r="F35" s="60"/>
@@ -4751,22 +4744,24 @@
         <v>243</v>
       </c>
       <c r="L35" s="60">
-        <v>47</v>
-      </c>
-      <c r="M35" s="60"/>
-    </row>
-    <row r="36" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="M35" s="60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A36" s="61" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B36" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>60</v>
+        <v>299</v>
       </c>
       <c r="D36" s="60" t="s">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="E36" s="60"/>
       <c r="F36" s="60"/>
@@ -4782,22 +4777,24 @@
         <v>243</v>
       </c>
       <c r="L36" s="60">
-        <v>48</v>
-      </c>
-      <c r="M36" s="60"/>
-    </row>
-    <row r="37" spans="1:13" ht="216" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="M36" s="60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="61" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B37" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C37" s="60" t="s">
-        <v>62</v>
+        <v>301</v>
       </c>
       <c r="D37" s="60" t="s">
-        <v>291</v>
+        <v>86</v>
       </c>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
@@ -4813,22 +4810,24 @@
         <v>243</v>
       </c>
       <c r="L37" s="60">
-        <v>49</v>
-      </c>
-      <c r="M37" s="60"/>
+        <v>64</v>
+      </c>
+      <c r="M37" s="60">
+        <v>5</v>
+      </c>
     </row>
     <row r="38" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A38" s="61" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B38" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D38" s="60" t="s">
-        <v>65</v>
+        <v>303</v>
       </c>
       <c r="E38" s="60"/>
       <c r="F38" s="60"/>
@@ -4844,22 +4843,24 @@
         <v>243</v>
       </c>
       <c r="L38" s="60">
-        <v>50</v>
-      </c>
-      <c r="M38" s="60"/>
-    </row>
-    <row r="39" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="M38" s="60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A39" s="61" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B39" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C39" s="60" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D39" s="60" t="s">
-        <v>294</v>
+        <v>90</v>
       </c>
       <c r="E39" s="60"/>
       <c r="F39" s="60"/>
@@ -4875,22 +4876,24 @@
         <v>243</v>
       </c>
       <c r="L39" s="60">
-        <v>51</v>
-      </c>
-      <c r="M39" s="60"/>
-    </row>
-    <row r="40" spans="1:13" ht="108" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="M39" s="60">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A40" s="61" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B40" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D40" s="60" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
@@ -4906,22 +4909,24 @@
         <v>243</v>
       </c>
       <c r="L40" s="60">
-        <v>52</v>
-      </c>
-      <c r="M40" s="60"/>
-    </row>
-    <row r="41" spans="1:13" ht="67.5" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="M40" s="60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A41" s="61" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B41" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>70</v>
+        <v>308</v>
       </c>
       <c r="D41" s="60" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="E41" s="60"/>
       <c r="F41" s="60"/>
@@ -4937,23 +4942,23 @@
         <v>243</v>
       </c>
       <c r="L41" s="60">
-        <v>53</v>
-      </c>
-      <c r="M41" s="60"/>
-    </row>
-    <row r="42" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="M41" s="60">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A42" s="61" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B42" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C42" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="60" t="s">
-        <v>300</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="D42" s="60"/>
       <c r="E42" s="60"/>
       <c r="F42" s="60"/>
       <c r="G42" s="60"/>
@@ -4961,30 +4966,32 @@
         <v>240</v>
       </c>
       <c r="I42" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J42" s="62"/>
+        <v>247</v>
+      </c>
+      <c r="J42" s="62" t="s">
+        <v>248</v>
+      </c>
       <c r="K42" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L42" s="60">
-        <v>54</v>
-      </c>
-      <c r="M42" s="60"/>
-    </row>
-    <row r="43" spans="1:13" ht="67.5" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="M42" s="60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A43" s="61" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B43" s="60" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C43" s="60" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" s="60" t="s">
-        <v>302</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="D43" s="60"/>
       <c r="E43" s="60"/>
       <c r="F43" s="60"/>
       <c r="G43" s="60"/>
@@ -4992,29 +4999,33 @@
         <v>240</v>
       </c>
       <c r="I43" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J43" s="62"/>
+        <v>247</v>
+      </c>
+      <c r="J43" s="62" t="s">
+        <v>248</v>
+      </c>
       <c r="K43" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L43" s="60">
-        <v>55</v>
-      </c>
-      <c r="M43" s="60"/>
-    </row>
-    <row r="44" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="M43" s="60">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A44" s="61" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B44" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>304</v>
+        <v>97</v>
       </c>
       <c r="D44" s="60" t="s">
-        <v>305</v>
+        <v>98</v>
       </c>
       <c r="E44" s="60"/>
       <c r="F44" s="60"/>
@@ -5030,24 +5041,24 @@
         <v>243</v>
       </c>
       <c r="L44" s="60">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="M44" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A45" s="61" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="B45" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C45" s="60" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D45" s="60" t="s">
-        <v>307</v>
+        <v>100</v>
       </c>
       <c r="E45" s="60"/>
       <c r="F45" s="60"/>
@@ -5063,24 +5074,24 @@
         <v>243</v>
       </c>
       <c r="L45" s="60">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="M45" s="60">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A46" s="61" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B46" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="D46" s="60" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="E46" s="60"/>
       <c r="F46" s="60"/>
@@ -5096,24 +5107,24 @@
         <v>243</v>
       </c>
       <c r="L46" s="60">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="M46" s="60">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A47" s="61" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B47" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C47" s="60" t="s">
-        <v>310</v>
+        <v>103</v>
       </c>
       <c r="D47" s="60" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E47" s="60"/>
       <c r="F47" s="60"/>
@@ -5129,24 +5140,24 @@
         <v>243</v>
       </c>
       <c r="L47" s="60">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="M47" s="60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A48" s="61" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B48" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D48" s="60" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E48" s="60"/>
       <c r="F48" s="60"/>
@@ -5162,24 +5173,24 @@
         <v>243</v>
       </c>
       <c r="L48" s="60">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="M48" s="60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A49" s="61" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B49" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C49" s="60" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D49" s="60" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E49" s="60"/>
       <c r="F49" s="60"/>
@@ -5195,24 +5206,24 @@
         <v>243</v>
       </c>
       <c r="L49" s="60">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M49" s="60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A50" s="61" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B50" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D50" s="60" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E50" s="60"/>
       <c r="F50" s="60"/>
@@ -5228,24 +5239,24 @@
         <v>243</v>
       </c>
       <c r="L50" s="60">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="M50" s="60">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A51" s="61" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B51" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C51" s="60" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D51" s="60" t="s">
-        <v>317</v>
+        <v>112</v>
       </c>
       <c r="E51" s="60"/>
       <c r="F51" s="60"/>
@@ -5261,24 +5272,24 @@
         <v>243</v>
       </c>
       <c r="L51" s="60">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="M51" s="60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A52" s="61" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B52" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>319</v>
+        <v>113</v>
       </c>
       <c r="D52" s="60" t="s">
-        <v>320</v>
+        <v>114</v>
       </c>
       <c r="E52" s="60"/>
       <c r="F52" s="60"/>
@@ -5294,23 +5305,25 @@
         <v>243</v>
       </c>
       <c r="L52" s="60">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="M52" s="60">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A53" s="61" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B53" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C53" s="60" t="s">
-        <v>322</v>
-      </c>
-      <c r="D53" s="60"/>
+        <v>115</v>
+      </c>
+      <c r="D53" s="60" t="s">
+        <v>116</v>
+      </c>
       <c r="E53" s="60"/>
       <c r="F53" s="60"/>
       <c r="G53" s="60"/>
@@ -5318,32 +5331,32 @@
         <v>240</v>
       </c>
       <c r="I53" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J53" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J53" s="62"/>
       <c r="K53" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L53" s="60">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="M53" s="60">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A54" s="61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B54" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>324</v>
-      </c>
-      <c r="D54" s="60"/>
+        <v>117</v>
+      </c>
+      <c r="D54" s="60" t="s">
+        <v>118</v>
+      </c>
       <c r="E54" s="60"/>
       <c r="F54" s="60"/>
       <c r="G54" s="60"/>
@@ -5351,33 +5364,31 @@
         <v>240</v>
       </c>
       <c r="I54" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J54" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J54" s="62"/>
       <c r="K54" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L54" s="60">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="M54" s="60">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A55" s="61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B55" s="60" t="s">
         <v>76</v>
       </c>
       <c r="C55" s="60" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="D55" s="60" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="E55" s="60"/>
       <c r="F55" s="60"/>
@@ -5393,24 +5404,24 @@
         <v>243</v>
       </c>
       <c r="L55" s="60">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M55" s="60">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A56" s="61" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B56" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="D56" s="60" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="E56" s="60"/>
       <c r="F56" s="60"/>
@@ -5426,24 +5437,24 @@
         <v>243</v>
       </c>
       <c r="L56" s="60">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="M56" s="60">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A57" s="61" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B57" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C57" s="60" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D57" s="60" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="E57" s="60"/>
       <c r="F57" s="60"/>
@@ -5459,24 +5470,24 @@
         <v>243</v>
       </c>
       <c r="L57" s="60">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="M57" s="60">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A58" s="61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B58" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="D58" s="60" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="E58" s="60"/>
       <c r="F58" s="60"/>
@@ -5492,24 +5503,24 @@
         <v>243</v>
       </c>
       <c r="L58" s="60">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="M58" s="60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="61" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B59" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C59" s="60" t="s">
-        <v>330</v>
+        <v>128</v>
       </c>
       <c r="D59" s="60" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E59" s="60"/>
       <c r="F59" s="60"/>
@@ -5525,24 +5536,24 @@
         <v>243</v>
       </c>
       <c r="L59" s="60">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M59" s="60">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A60" s="61" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B60" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C60" s="60" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="D60" s="60" t="s">
-        <v>332</v>
+        <v>131</v>
       </c>
       <c r="E60" s="60"/>
       <c r="F60" s="60"/>
@@ -5558,10 +5569,10 @@
         <v>243</v>
       </c>
       <c r="L60" s="60">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M60" s="60">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
@@ -5569,13 +5580,13 @@
         <v>333</v>
       </c>
       <c r="B61" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C61" s="60" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="D61" s="60" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="E61" s="60"/>
       <c r="F61" s="60"/>
@@ -5591,24 +5602,24 @@
         <v>243</v>
       </c>
       <c r="L61" s="60">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M61" s="60">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A62" s="61" t="s">
         <v>334</v>
       </c>
       <c r="B62" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C62" s="60" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="D62" s="60" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E62" s="60"/>
       <c r="F62" s="60"/>
@@ -5624,24 +5635,24 @@
         <v>243</v>
       </c>
       <c r="L62" s="60">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M62" s="60">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A63" s="61" t="s">
         <v>335</v>
       </c>
       <c r="B63" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C63" s="60" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="D63" s="60" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="E63" s="60"/>
       <c r="F63" s="60"/>
@@ -5657,24 +5668,24 @@
         <v>243</v>
       </c>
       <c r="L63" s="60">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M63" s="60">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="162" x14ac:dyDescent="0.25">
       <c r="A64" s="61" t="s">
         <v>336</v>
       </c>
       <c r="B64" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C64" s="60" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="D64" s="60" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="E64" s="60"/>
       <c r="F64" s="60"/>
@@ -5690,24 +5701,24 @@
         <v>243</v>
       </c>
       <c r="L64" s="60">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="M64" s="60">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="94.5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A65" s="61" t="s">
         <v>337</v>
       </c>
       <c r="B65" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C65" s="60" t="s">
-        <v>117</v>
+        <v>338</v>
       </c>
       <c r="D65" s="60" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E65" s="60"/>
       <c r="F65" s="60"/>
@@ -5723,24 +5734,24 @@
         <v>243</v>
       </c>
       <c r="L65" s="60">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="M65" s="60">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A66" s="61" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B66" s="60" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C66" s="60" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="D66" s="60" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="E66" s="60"/>
       <c r="F66" s="60"/>
@@ -5756,24 +5767,24 @@
         <v>243</v>
       </c>
       <c r="L66" s="60">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="M66" s="60">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A67" s="61" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B67" s="60" t="s">
         <v>121</v>
       </c>
       <c r="C67" s="60" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="D67" s="60" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="E67" s="60"/>
       <c r="F67" s="60"/>
@@ -5789,24 +5800,24 @@
         <v>243</v>
       </c>
       <c r="L67" s="60">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="M67" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A68" s="61" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B68" s="60" t="s">
         <v>121</v>
       </c>
       <c r="C68" s="60" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="D68" s="60" t="s">
-        <v>125</v>
+        <v>342</v>
       </c>
       <c r="E68" s="60"/>
       <c r="F68" s="60"/>
@@ -5822,24 +5833,24 @@
         <v>243</v>
       </c>
       <c r="L68" s="60">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="M68" s="60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A69" s="61" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B69" s="60" t="s">
         <v>121</v>
       </c>
       <c r="C69" s="60" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="D69" s="60" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E69" s="60"/>
       <c r="F69" s="60"/>
@@ -5855,24 +5866,24 @@
         <v>243</v>
       </c>
       <c r="L69" s="60">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M69" s="60">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A70" s="61" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B70" s="60" t="s">
         <v>121</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D70" s="60" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E70" s="60"/>
       <c r="F70" s="60"/>
@@ -5888,24 +5899,24 @@
         <v>243</v>
       </c>
       <c r="L70" s="60">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="M70" s="60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="216" x14ac:dyDescent="0.25">
       <c r="A71" s="61" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B71" s="60" t="s">
         <v>121</v>
       </c>
       <c r="C71" s="60" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="D71" s="60" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E71" s="60"/>
       <c r="F71" s="60"/>
@@ -5921,24 +5932,24 @@
         <v>243</v>
       </c>
       <c r="L71" s="60">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="M71" s="60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A72" s="61" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B72" s="60" t="s">
         <v>121</v>
       </c>
       <c r="C72" s="60" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="D72" s="60" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="E72" s="60"/>
       <c r="F72" s="60"/>
@@ -5954,24 +5965,24 @@
         <v>243</v>
       </c>
       <c r="L72" s="60">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="M72" s="60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="61" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B73" s="60" t="s">
         <v>121</v>
       </c>
       <c r="C73" s="60" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="D73" s="60" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E73" s="60"/>
       <c r="F73" s="60"/>
@@ -5987,24 +5998,24 @@
         <v>243</v>
       </c>
       <c r="L73" s="60">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M73" s="60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A74" s="61" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B74" s="60" t="s">
         <v>121</v>
       </c>
       <c r="C74" s="60" t="s">
-        <v>136</v>
+        <v>349</v>
       </c>
       <c r="D74" s="60" t="s">
-        <v>137</v>
+        <v>350</v>
       </c>
       <c r="E74" s="60"/>
       <c r="F74" s="60"/>
@@ -6020,24 +6031,24 @@
         <v>243</v>
       </c>
       <c r="L74" s="60">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="M74" s="60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="162" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A75" s="61" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B75" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C75" s="60" t="s">
-        <v>138</v>
+        <v>352</v>
       </c>
       <c r="D75" s="60" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="E75" s="60"/>
       <c r="F75" s="60"/>
@@ -6053,24 +6064,24 @@
         <v>243</v>
       </c>
       <c r="L75" s="60">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="M75" s="60">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A76" s="61" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B76" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C76" s="60" t="s">
-        <v>349</v>
+        <v>163</v>
       </c>
       <c r="D76" s="60" t="s">
-        <v>141</v>
+        <v>354</v>
       </c>
       <c r="E76" s="60"/>
       <c r="F76" s="60"/>
@@ -6086,24 +6097,24 @@
         <v>243</v>
       </c>
       <c r="L76" s="60">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="M76" s="60">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A77" s="61" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B77" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C77" s="60" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="D77" s="60" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="E77" s="60"/>
       <c r="F77" s="60"/>
@@ -6119,24 +6130,24 @@
         <v>243</v>
       </c>
       <c r="L77" s="60">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="M77" s="60">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A78" s="61" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B78" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C78" s="60" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="D78" s="60" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="E78" s="60"/>
       <c r="F78" s="60"/>
@@ -6152,24 +6163,24 @@
         <v>243</v>
       </c>
       <c r="L78" s="60">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="M78" s="60">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A79" s="61" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B79" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C79" s="60" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="D79" s="60" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E79" s="60"/>
       <c r="F79" s="60"/>
@@ -6185,24 +6196,24 @@
         <v>243</v>
       </c>
       <c r="L79" s="60">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="M79" s="60">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A80" s="61" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B80" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C80" s="60" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="D80" s="60" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="E80" s="60"/>
       <c r="F80" s="60"/>
@@ -6218,24 +6229,24 @@
         <v>243</v>
       </c>
       <c r="L80" s="60">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="M80" s="60">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A81" s="61" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B81" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C81" s="60" t="s">
-        <v>150</v>
+        <v>361</v>
       </c>
       <c r="D81" s="60" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="E81" s="60"/>
       <c r="F81" s="60"/>
@@ -6251,24 +6262,24 @@
         <v>243</v>
       </c>
       <c r="L81" s="60">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="M81" s="60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="216" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A82" s="61" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B82" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C82" s="60" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="D82" s="60" t="s">
-        <v>153</v>
+        <v>363</v>
       </c>
       <c r="E82" s="60"/>
       <c r="F82" s="60"/>
@@ -6284,24 +6295,24 @@
         <v>243</v>
       </c>
       <c r="L82" s="60">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="M82" s="60">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A83" s="61" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B83" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C83" s="60" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="D83" s="60" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="E83" s="60"/>
       <c r="F83" s="60"/>
@@ -6317,24 +6328,24 @@
         <v>243</v>
       </c>
       <c r="L83" s="60">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="M83" s="60">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A84" s="61" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B84" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C84" s="60" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="D84" s="60" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="E84" s="60"/>
       <c r="F84" s="60"/>
@@ -6350,24 +6361,24 @@
         <v>243</v>
       </c>
       <c r="L84" s="60">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="M84" s="60">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A85" s="61" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B85" s="60" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="C85" s="60" t="s">
-        <v>360</v>
+        <v>181</v>
       </c>
       <c r="D85" s="60" t="s">
-        <v>361</v>
+        <v>182</v>
       </c>
       <c r="E85" s="60"/>
       <c r="F85" s="60"/>
@@ -6383,24 +6394,24 @@
         <v>243</v>
       </c>
       <c r="L85" s="60">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="M85" s="60">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A86" s="61" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B86" s="60" t="s">
         <v>160</v>
       </c>
       <c r="C86" s="60" t="s">
-        <v>363</v>
+        <v>183</v>
       </c>
       <c r="D86" s="60" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E86" s="60"/>
       <c r="F86" s="60"/>
@@ -6416,24 +6427,24 @@
         <v>243</v>
       </c>
       <c r="L86" s="60">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="M86" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="61" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B87" s="60" t="s">
         <v>160</v>
       </c>
       <c r="C87" s="60" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="D87" s="60" t="s">
-        <v>365</v>
+        <v>186</v>
       </c>
       <c r="E87" s="60"/>
       <c r="F87" s="60"/>
@@ -6449,24 +6460,24 @@
         <v>243</v>
       </c>
       <c r="L87" s="60">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="M87" s="60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A88" s="61" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B88" s="60" t="s">
         <v>160</v>
       </c>
       <c r="C88" s="60" t="s">
-        <v>165</v>
+        <v>370</v>
       </c>
       <c r="D88" s="60" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="E88" s="60"/>
       <c r="F88" s="60"/>
@@ -6482,24 +6493,24 @@
         <v>243</v>
       </c>
       <c r="L88" s="60">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="M88" s="60">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A89" s="61" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B89" s="60" t="s">
         <v>160</v>
       </c>
       <c r="C89" s="60" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="D89" s="60" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="E89" s="60"/>
       <c r="F89" s="60"/>
@@ -6515,24 +6526,24 @@
         <v>243</v>
       </c>
       <c r="L89" s="60">
-        <v>109</v>
-      </c>
-      <c r="M89" s="60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="M89" s="60" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A90" s="61" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B90" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C90" s="60" t="s">
-        <v>169</v>
+        <v>374</v>
       </c>
       <c r="D90" s="60" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E90" s="60"/>
       <c r="F90" s="60"/>
@@ -6545,27 +6556,27 @@
       </c>
       <c r="J90" s="62"/>
       <c r="K90" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L90" s="60">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="M90" s="60">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A91" s="61" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B91" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C91" s="60" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="D91" s="60" t="s">
-        <v>172</v>
+        <v>378</v>
       </c>
       <c r="E91" s="60"/>
       <c r="F91" s="60"/>
@@ -6578,27 +6589,25 @@
       </c>
       <c r="J91" s="62"/>
       <c r="K91" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L91" s="60">
-        <v>111</v>
-      </c>
-      <c r="M91" s="60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="M91" s="60"/>
+    </row>
+    <row r="92" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A92" s="61" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B92" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C92" s="60" t="s">
-        <v>372</v>
+        <v>196</v>
       </c>
       <c r="D92" s="60" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="E92" s="60"/>
       <c r="F92" s="60"/>
@@ -6611,27 +6620,27 @@
       </c>
       <c r="J92" s="62"/>
       <c r="K92" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L92" s="60">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="M92" s="60">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A93" s="61" t="s">
+        <v>380</v>
+      </c>
+      <c r="B93" s="60" t="s">
         <v>373</v>
       </c>
-      <c r="B93" s="60" t="s">
-        <v>160</v>
-      </c>
       <c r="C93" s="60" t="s">
-        <v>175</v>
+        <v>381</v>
       </c>
       <c r="D93" s="60" t="s">
-        <v>374</v>
+        <v>199</v>
       </c>
       <c r="E93" s="60"/>
       <c r="F93" s="60"/>
@@ -6644,27 +6653,27 @@
       </c>
       <c r="J93" s="62"/>
       <c r="K93" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L93" s="60">
-        <v>113</v>
+        <v>5</v>
       </c>
       <c r="M93" s="60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A94" s="61" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B94" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C94" s="60" t="s">
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="D94" s="60" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="E94" s="60"/>
       <c r="F94" s="60"/>
@@ -6677,27 +6686,27 @@
       </c>
       <c r="J94" s="62"/>
       <c r="K94" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L94" s="60">
-        <v>114</v>
+        <v>6</v>
       </c>
       <c r="M94" s="60">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A95" s="61" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B95" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C95" s="60" t="s">
-        <v>179</v>
+        <v>385</v>
       </c>
       <c r="D95" s="60" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="E95" s="60"/>
       <c r="F95" s="60"/>
@@ -6710,27 +6719,27 @@
       </c>
       <c r="J95" s="62"/>
       <c r="K95" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L95" s="60">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="M95" s="60">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A96" s="61" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B96" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C96" s="60" t="s">
-        <v>181</v>
+        <v>387</v>
       </c>
       <c r="D96" s="60" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="E96" s="60"/>
       <c r="F96" s="60"/>
@@ -6743,27 +6752,27 @@
       </c>
       <c r="J96" s="62"/>
       <c r="K96" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L96" s="60">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="M96" s="60">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A97" s="61" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B97" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C97" s="60" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="D97" s="60" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="E97" s="60"/>
       <c r="F97" s="60"/>
@@ -6776,27 +6785,27 @@
       </c>
       <c r="J97" s="62"/>
       <c r="K97" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L97" s="60">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="M97" s="60">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A98" s="61" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B98" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C98" s="60" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D98" s="60" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E98" s="60"/>
       <c r="F98" s="60"/>
@@ -6809,27 +6818,27 @@
       </c>
       <c r="J98" s="62"/>
       <c r="K98" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L98" s="60">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="M98" s="60">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A99" s="61" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="B99" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C99" s="60" t="s">
-        <v>381</v>
+        <v>209</v>
       </c>
       <c r="D99" s="60" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="E99" s="60"/>
       <c r="F99" s="60"/>
@@ -6842,27 +6851,27 @@
       </c>
       <c r="J99" s="62"/>
       <c r="K99" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L99" s="60">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="M99" s="60">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A100" s="61" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B100" s="60" t="s">
-        <v>160</v>
+        <v>373</v>
       </c>
       <c r="C100" s="60" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="D100" s="60" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="E100" s="60"/>
       <c r="F100" s="60"/>
@@ -6875,27 +6884,27 @@
       </c>
       <c r="J100" s="62"/>
       <c r="K100" s="60" t="s">
-        <v>243</v>
+        <v>376</v>
       </c>
       <c r="L100" s="60">
-        <v>120</v>
-      </c>
-      <c r="M100" s="60" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="M100" s="60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A101" s="61" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B101" s="60" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C101" s="60" t="s">
-        <v>385</v>
+        <v>213</v>
       </c>
       <c r="D101" s="60" t="s">
-        <v>386</v>
+        <v>199</v>
       </c>
       <c r="E101" s="60"/>
       <c r="F101" s="60"/>
@@ -6908,27 +6917,27 @@
       </c>
       <c r="J101" s="62"/>
       <c r="K101" s="60" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L101" s="60">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M101" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A102" s="61" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B102" s="60" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C102" s="60" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="D102" s="60" t="s">
-        <v>389</v>
+        <v>215</v>
       </c>
       <c r="E102" s="60"/>
       <c r="F102" s="60"/>
@@ -6941,25 +6950,27 @@
       </c>
       <c r="J102" s="62"/>
       <c r="K102" s="60" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L102" s="60">
-        <v>3</v>
-      </c>
-      <c r="M102" s="60"/>
-    </row>
-    <row r="103" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="M102" s="60">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A103" s="61" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B103" s="60" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C103" s="60" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="D103" s="60" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="E103" s="60"/>
       <c r="F103" s="60"/>
@@ -6972,27 +6983,27 @@
       </c>
       <c r="J103" s="62"/>
       <c r="K103" s="60" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L103" s="60">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M103" s="60">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A104" s="61" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B104" s="60" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C104" s="60" t="s">
-        <v>392</v>
+        <v>217</v>
       </c>
       <c r="D104" s="60" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="E104" s="60"/>
       <c r="F104" s="60"/>
@@ -7005,27 +7016,27 @@
       </c>
       <c r="J104" s="62"/>
       <c r="K104" s="60" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L104" s="60">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M104" s="60">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A105" s="61" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B105" s="60" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C105" s="60" t="s">
-        <v>394</v>
+        <v>219</v>
       </c>
       <c r="D105" s="60" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="E105" s="60"/>
       <c r="F105" s="60"/>
@@ -7038,27 +7049,27 @@
       </c>
       <c r="J105" s="62"/>
       <c r="K105" s="60" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L105" s="60">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M105" s="60">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A106" s="61" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B106" s="60" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C106" s="60" t="s">
-        <v>396</v>
+        <v>221</v>
       </c>
       <c r="D106" s="60" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="E106" s="60"/>
       <c r="F106" s="60"/>
@@ -7071,27 +7082,27 @@
       </c>
       <c r="J106" s="62"/>
       <c r="K106" s="60" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L106" s="60">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M106" s="60">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A107" s="61" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B107" s="60" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="C107" s="60" t="s">
-        <v>398</v>
+        <v>223</v>
       </c>
       <c r="D107" s="60" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="E107" s="60"/>
       <c r="F107" s="60"/>
@@ -7104,384 +7115,21 @@
       </c>
       <c r="J107" s="62"/>
       <c r="K107" s="60" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="L107" s="60">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M107" s="60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A108" s="61" t="s">
-        <v>399</v>
-      </c>
-      <c r="B108" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C108" s="60" t="s">
-        <v>205</v>
-      </c>
-      <c r="D108" s="60" t="s">
-        <v>206</v>
-      </c>
-      <c r="E108" s="60"/>
-      <c r="F108" s="60"/>
-      <c r="G108" s="60"/>
-      <c r="H108" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I108" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J108" s="62"/>
-      <c r="K108" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L108" s="60">
-        <v>9</v>
-      </c>
-      <c r="M108" s="60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A109" s="61" t="s">
-        <v>400</v>
-      </c>
-      <c r="B109" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C109" s="60" t="s">
-        <v>207</v>
-      </c>
-      <c r="D109" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="E109" s="60"/>
-      <c r="F109" s="60"/>
-      <c r="G109" s="60"/>
-      <c r="H109" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I109" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J109" s="62"/>
-      <c r="K109" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L109" s="60">
-        <v>10</v>
-      </c>
-      <c r="M109" s="60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A110" s="61" t="s">
-        <v>401</v>
-      </c>
-      <c r="B110" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C110" s="60" t="s">
-        <v>209</v>
-      </c>
-      <c r="D110" s="60" t="s">
-        <v>210</v>
-      </c>
-      <c r="E110" s="60"/>
-      <c r="F110" s="60"/>
-      <c r="G110" s="60"/>
-      <c r="H110" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I110" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J110" s="62"/>
-      <c r="K110" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L110" s="60">
-        <v>11</v>
-      </c>
-      <c r="M110" s="60">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A111" s="61" t="s">
-        <v>402</v>
-      </c>
-      <c r="B111" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C111" s="60" t="s">
-        <v>211</v>
-      </c>
-      <c r="D111" s="60" t="s">
-        <v>212</v>
-      </c>
-      <c r="E111" s="60"/>
-      <c r="F111" s="60"/>
-      <c r="G111" s="60"/>
-      <c r="H111" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I111" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J111" s="62"/>
-      <c r="K111" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L111" s="60">
-        <v>12</v>
-      </c>
-      <c r="M111" s="60">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A112" s="61" t="s">
-        <v>403</v>
-      </c>
-      <c r="B112" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C112" s="60" t="s">
-        <v>213</v>
-      </c>
-      <c r="D112" s="60" t="s">
-        <v>199</v>
-      </c>
-      <c r="E112" s="60"/>
-      <c r="F112" s="60"/>
-      <c r="G112" s="60"/>
-      <c r="H112" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I112" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J112" s="62"/>
-      <c r="K112" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L112" s="60">
-        <v>13</v>
-      </c>
-      <c r="M112" s="60">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A113" s="61" t="s">
-        <v>404</v>
-      </c>
-      <c r="B113" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C113" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="D113" s="60" t="s">
-        <v>215</v>
-      </c>
-      <c r="E113" s="60"/>
-      <c r="F113" s="60"/>
-      <c r="G113" s="60"/>
-      <c r="H113" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I113" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J113" s="62"/>
-      <c r="K113" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L113" s="60">
-        <v>14</v>
-      </c>
-      <c r="M113" s="60">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="61" t="s">
-        <v>405</v>
-      </c>
-      <c r="B114" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C114" s="60" t="s">
-        <v>216</v>
-      </c>
-      <c r="D114" s="60" t="s">
-        <v>215</v>
-      </c>
-      <c r="E114" s="60"/>
-      <c r="F114" s="60"/>
-      <c r="G114" s="60"/>
-      <c r="H114" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I114" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J114" s="62"/>
-      <c r="K114" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L114" s="60">
-        <v>15</v>
-      </c>
-      <c r="M114" s="60">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A115" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="B115" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C115" s="60" t="s">
-        <v>217</v>
-      </c>
-      <c r="D115" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="E115" s="60"/>
-      <c r="F115" s="60"/>
-      <c r="G115" s="60"/>
-      <c r="H115" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I115" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J115" s="62"/>
-      <c r="K115" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L115" s="60">
-        <v>16</v>
-      </c>
-      <c r="M115" s="60">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A116" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="B116" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C116" s="60" t="s">
-        <v>219</v>
-      </c>
-      <c r="D116" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="E116" s="60"/>
-      <c r="F116" s="60"/>
-      <c r="G116" s="60"/>
-      <c r="H116" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I116" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J116" s="62"/>
-      <c r="K116" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L116" s="60">
-        <v>17</v>
-      </c>
-      <c r="M116" s="60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A117" s="61" t="s">
-        <v>408</v>
-      </c>
-      <c r="B117" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C117" s="60" t="s">
-        <v>221</v>
-      </c>
-      <c r="D117" s="60" t="s">
-        <v>222</v>
-      </c>
-      <c r="E117" s="60"/>
-      <c r="F117" s="60"/>
-      <c r="G117" s="60"/>
-      <c r="H117" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I117" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J117" s="62"/>
-      <c r="K117" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L117" s="60">
-        <v>18</v>
-      </c>
-      <c r="M117" s="60">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A118" s="61" t="s">
-        <v>409</v>
-      </c>
-      <c r="B118" s="60" t="s">
-        <v>384</v>
-      </c>
-      <c r="C118" s="60" t="s">
-        <v>223</v>
-      </c>
-      <c r="D118" s="60" t="s">
-        <v>224</v>
-      </c>
-      <c r="E118" s="60"/>
-      <c r="F118" s="60"/>
-      <c r="G118" s="60"/>
-      <c r="H118" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I118" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J118" s="62"/>
-      <c r="K118" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="L118" s="60">
-        <v>19</v>
-      </c>
-      <c r="M118" s="60">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="B2:B118" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="B2:B107" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Ерөнхий,Даатгалын хяналтын чиглэлээс,ХЗХХЧ-ээс,ХОҮЭХЧ-ээс,ХЗХГ,МУТА,ВХҮҮ,Сургалт"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2:I118" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="I2:I107" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"draft,needs_answer,needs_review,ready"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7513,19 +7161,19 @@
   <sheetData>
     <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="58" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="F1" s="58" t="s">
         <v>229</v>
@@ -7537,7 +7185,7 @@
         <v>233</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -7550,7 +7198,7 @@
       <c r="G2" s="59"/>
       <c r="H2" s="59"/>
       <c r="J2" s="60" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">

--- a/outputs/faq-chatbot/FAQ_Chatbot_Data.xlsx
+++ b/outputs/faq-chatbot/FAQ_Chatbot_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frcmongolia-my.sharepoint.com/personal/delgermaa_frc_mn/Documents/Documents/GitHub/frc_frontend/outputs/faq-chatbot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_CD600E785A1BBF5C12BC81CD29DD7CE5B966D982" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5595F1DA-973B-45C1-8F86-1236D433883B}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_CD600E785A1BBF5C12BC81CD29DD7CE5B966D982" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14726E3D-87E8-4FC8-A3DB-F28601A73ABD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="400">
   <si>
     <t>№</t>
   </si>
@@ -912,34 +912,16 @@
     <t>Тус ХЗХ-ны талаарх тодохройлолтыг СЗХ-оос  авч УБЕГ-т хандана.</t>
   </si>
   <si>
-    <t>faq-032</t>
-  </si>
-  <si>
     <t>faq-033</t>
   </si>
   <si>
     <t>Зээлийн гэрээний хугацаанд зээлээ төлөлгүй 30-90, 90-180, 180-360, 360-аас дээш хоног хэтэрсэн бол таны зээлийн мэдээллийн санд зээлийн ангилал буурч өөрчлөгдөн хадгалагдах болно.</t>
   </si>
   <si>
-    <t>faq-034</t>
-  </si>
-  <si>
     <t>faq-035</t>
   </si>
   <si>
     <t>Даатгалын хураамж гэж даатгуулагч даатгалын зүйлээ даатгуулсны төлөө даатгагчид төлөх төлбөрийг хэлнэ.</t>
-  </si>
-  <si>
-    <t>faq-036</t>
-  </si>
-  <si>
-    <t>Компанийн энгийн хувьцаа эзэмшигч нь дараах эрх эдэлнэ: 
-- хувьцаа эзэмшигчдийн хуралд оролцож, хурлаар хэлэлцэж байгаа бүх асуудлаар өөрийн эзэмшлийн хувьцааны тоотой хувь тэнцүүлэн санал өгөх;
-- ногдол ашиг авах;
-- хувьцаат компанийн энгийн хувьцаа эзэмшигч нь энэ хуулийн 38 дугаар зүйл болон компанийн дүрэмд заасны дагуу компаниас нэмж гаргах хувьцаа, түүнд хамаарах үнэт цаасыг тэргүүн ээлжид худалдан авах эрхтэй;
-- хувьцаат компани нь жилийн санхүүгийн болон үйл ажиллагааны тайлан, компанийн нэгдмэл сонирхолтой этгээдийн нэр, тэдгээрийн эзэмшлийн хувьцааны төрөл, тоо болон Санхүүгийн зохицуулах хороо болон үнэт цаасны арилжаа эрхлэх байгууллагын дүрэм, журмаар тогтоосон бусад мэдээлэлтэй танилцах;
-- таны хуулиар олгогдсон эрхийг хязгаарласан шийдвэр гаргасан болон Компанийн тухай хуульд заасан зарим тохиолдолуудад өөрийн эзэмшлийн хувьцааг эргүүлэн худалдаж авахыг компаниас шаардах эрхтэй;
-- компанийг татан буулгах үед тогтоосон журмын дагуу үлдсэн эд хөрөнгийг худалдсанаас олсон орлогоос хувь хүртэх.</t>
   </si>
   <si>
     <t>faq-037</t>
@@ -963,23 +945,6 @@
 Даатгалын гэрээнд тусгасан дээрх нөхцөлүүдтэй сайтар уншиж танилцсанаар гарын үсэг зурж баталгаажуулах.</t>
   </si>
   <si>
-    <t>faq-040</t>
-  </si>
-  <si>
-    <t>Даатгагч болон холбогдох эрх бүхий байгууллагын утсанд дуудлага өгөх
-Дуудлага өгөх боломжгүй нөхцөлд орчны зураг авах, бичлэг хийж даатгалын тохиолдлыг баталгаажуулах
-Даатгалын тохиолдол болсон үед гэрээний нөхцөлийн дагуу нөхөн төлбөр олгохыг даатгагчаас шаардах</t>
-  </si>
-  <si>
-    <t>faq-041</t>
-  </si>
-  <si>
-    <t>Даатгалын баталгааны эх хувь
-Даатгуулагчийн өргөдөл
-Эрх бүхий этгээдийн гаргасан дүгнэлт, акт, материал
-Шаардлагатай тохиолдолд мэргэжлийн байгууллагын гаргасан дүгнэлт /эмнэлэг, цагдаа г.м/</t>
-  </si>
-  <si>
     <t>faq-042</t>
   </si>
   <si>
@@ -1011,27 +976,12 @@
     <t>Хуулийн этгээдийн улсын бүртгэлд бүртгүүлснээс хойш хэд хоногт багтааж хадгаламж, зээлийн үйл ажиллагаа эрхлэх тусгай зөвшөөрөл авах хүсэлтээ СЗХ-нд хүргүүлэх вэ?</t>
   </si>
   <si>
-    <t>faq-047</t>
-  </si>
-  <si>
-    <t>Зөвшөөрлийн хүсэлт, баримт бичгийг цахим системд яаж бүртгүүлэх вэ?</t>
-  </si>
-  <si>
     <t>faq-048</t>
   </si>
   <si>
     <t>Баримт бичгийн бүрдэл хангасан эсэхийг ажлын 2 хоногийн дотор шалгана, бүрдэл хангаагүй дутуу бол ажлын 30 хоногт багтаан нөхөн бүрдүүлэх талаар хариу хүргүүлнэ. Бүрдэл хангасан бол ажлын 10 өдрийн дотор магадлан шалгана хангасан тохиолдолд ажлын 5 өдөрт багтаан шийдвэрлэнэ. Мөн дүгнэлт, тодорхойлолт гаргуулах бол ажлын 5 өдөр сунгаж болно.</t>
   </si>
   <si>
-    <t>faq-049</t>
-  </si>
-  <si>
-    <t>faq-050</t>
-  </si>
-  <si>
-    <t>Санхүүгийн зохицуулах хорооны мэдээллийн технологийн хэлтэс itd.frc.mn цахим хаягт хүсэлт илгээх эсвэл 51-263425 дугаарт холбогдох.</t>
-  </si>
-  <si>
     <t>faq-051</t>
   </si>
   <si>
@@ -1041,18 +991,6 @@
     <t>СЗХ-ны www.frc.mn цахим хуудаст зохицуулалтын салбар цэсний  хадгаламж зээлийн хоршоог сонгон нэвтэрч зөвшөөрлийн цахим систем рүү дарж орон журам, бүрдүүлэх баримт бичиг, баримт бичиг бүрдүүлэх заавар, маягтын хэсгийг үзнэ үү.</t>
   </si>
   <si>
-    <t>faq-052</t>
-  </si>
-  <si>
-    <t>Хаяг байршлын өөрчлөлтийг бүртгүүлэх ямар баримт бичиг бүрдүүлэх вэ?</t>
-  </si>
-  <si>
-    <t>faq-053</t>
-  </si>
-  <si>
-    <t>Гүйцэтгэх захирлын өөрчлөлтийг бүртгүүлэх ямар баримт бичиг бүрдүүлэх вэ?</t>
-  </si>
-  <si>
     <t>faq-054</t>
   </si>
   <si>
@@ -1062,9 +1000,6 @@
     <t>faq-056</t>
   </si>
   <si>
-    <t>faq-057</t>
-  </si>
-  <si>
     <t>faq-058</t>
   </si>
   <si>
@@ -1083,12 +1018,6 @@
     <t>faq-061</t>
   </si>
   <si>
-    <t>faq-062</t>
-  </si>
-  <si>
-    <t>faq-063</t>
-  </si>
-  <si>
     <t>faq-064</t>
   </si>
   <si>
@@ -1120,12 +1049,6 @@
   </si>
   <si>
     <t>faq-074</t>
-  </si>
-  <si>
-    <t>faq-075</t>
-  </si>
-  <si>
-    <t>Дотоод хяналтын хөтөлбөрийн загвар, жишиг хөтөлбөрийг хаанаас үзэх вэ?</t>
   </si>
   <si>
     <t>faq-076</t>
@@ -1219,15 +1142,6 @@
     <t>faq-097</t>
   </si>
   <si>
-    <t>faq-098</t>
-  </si>
-  <si>
-    <t>Үйл ажиллагааны тайлан өгөх хугацаа</t>
-  </si>
-  <si>
-    <t>faq-099</t>
-  </si>
-  <si>
     <t>faq-100</t>
   </si>
   <si>
@@ -1355,6 +1269,36 @@
   </si>
   <si>
     <t xml:space="preserve">Даатгал </t>
+  </si>
+  <si>
+    <t>Мөнгө угаахтай тэмцэх</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Виртуал хөрөнгийн үйлчилгээ үзүүлэгч </t>
+  </si>
+  <si>
+    <t>Хороонд хүсэлтээ өгөөд бүртгүүлэх хүртлээ байршуулсан байх шаардлагатай</t>
+  </si>
+  <si>
+    <t>Хадгаламж зээлийн хоршоо</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Хяналт шалгалт </t>
+  </si>
+  <si>
+    <t xml:space="preserve">холбоо барих </t>
+  </si>
+  <si>
+    <t>Өргөдөл гомдол</t>
+  </si>
+  <si>
+    <t>салбар</t>
+  </si>
+  <si>
+    <t>үнэт цаас</t>
+  </si>
+  <si>
+    <t>хөрөнгийн зах зээл</t>
   </si>
 </sst>
 </file>
@@ -1899,6 +1843,9 @@
     <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1919,9 +1866,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1946,8 +1890,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FaqDataTable" displayName="FaqDataTable" ref="A1:M107" totalsRowShown="0">
-  <autoFilter ref="A1:M107" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FaqDataTable" displayName="FaqDataTable" ref="A1:M91" totalsRowShown="0">
+  <autoFilter ref="A1:M91" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="faq_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category"/>
@@ -2698,11 +2642,11 @@
       <c r="C57" s="22"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="70" t="s">
+      <c r="A59" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="B59" s="70"/>
-      <c r="C59" s="70"/>
+      <c r="B59" s="71"/>
+      <c r="C59" s="71"/>
     </row>
     <row r="60" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="38">
@@ -2799,7 +2743,7 @@
       <c r="B68" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="C68" s="64" t="s">
+      <c r="C68" s="65" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2810,7 +2754,7 @@
       <c r="B69" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="C69" s="64"/>
+      <c r="C69" s="65"/>
     </row>
     <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="38">
@@ -2819,7 +2763,7 @@
       <c r="B70" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="C70" s="65"/>
+      <c r="C70" s="66"/>
     </row>
     <row r="71" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="38">
@@ -2954,11 +2898,11 @@
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="66" t="s">
+      <c r="A84" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="B84" s="67"/>
-      <c r="C84" s="68"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="69"/>
     </row>
     <row r="85" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="41">
@@ -3177,11 +3121,11 @@
       <c r="C104" s="47"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="69" t="s">
+      <c r="A105" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="B105" s="69"/>
-      <c r="C105" s="69"/>
+      <c r="B105" s="70"/>
+      <c r="C105" s="70"/>
     </row>
     <row r="106" spans="1:3" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A106" s="41">
@@ -3589,13 +3533,13 @@
   <sheetPr>
     <tabColor rgb="FF2957A4"/>
   </sheetPr>
-  <dimension ref="A1:M107"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="58" customWidth="1"/>
-    <col min="4" max="4" width="82" style="71" customWidth="1"/>
+    <col min="4" max="4" width="82" style="64" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="6" width="42" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
@@ -3656,12 +3600,14 @@
         <v>239</v>
       </c>
       <c r="C2" s="60" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="D2" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="60"/>
+      <c r="E2" s="60" t="s">
+        <v>395</v>
+      </c>
       <c r="F2" s="60"/>
       <c r="G2" s="60"/>
       <c r="H2" s="60" t="s">
@@ -3696,7 +3642,9 @@
       <c r="D3" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="60"/>
+      <c r="E3" s="60" t="s">
+        <v>396</v>
+      </c>
       <c r="F3" s="60"/>
       <c r="G3" s="60"/>
       <c r="H3" s="60" t="s">
@@ -3727,9 +3675,11 @@
         <v>7</v>
       </c>
       <c r="D4" s="60" t="s">
-        <v>407</v>
-      </c>
-      <c r="E4" s="60"/>
+        <v>382</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>397</v>
+      </c>
       <c r="F4" s="60"/>
       <c r="G4" s="60"/>
       <c r="H4" s="60" t="s">
@@ -3756,7 +3706,7 @@
         <v>249</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="C5" s="60" t="s">
         <v>8</v>
@@ -3764,7 +3714,9 @@
       <c r="D5" s="60" t="s">
         <v>250</v>
       </c>
-      <c r="E5" s="60"/>
+      <c r="E5" s="60" t="s">
+        <v>398</v>
+      </c>
       <c r="F5" s="60"/>
       <c r="G5" s="60"/>
       <c r="H5" s="60" t="s">
@@ -3789,7 +3741,7 @@
         <v>251</v>
       </c>
       <c r="B6" s="60" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="C6" s="60" t="s">
         <v>10</v>
@@ -3797,7 +3749,9 @@
       <c r="D6" s="60" t="s">
         <v>252</v>
       </c>
-      <c r="E6" s="60"/>
+      <c r="E6" s="60" t="s">
+        <v>399</v>
+      </c>
       <c r="F6" s="60"/>
       <c r="G6" s="60"/>
       <c r="H6" s="60" t="s">
@@ -3822,13 +3776,13 @@
         <v>253</v>
       </c>
       <c r="B7" s="60" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="C7" s="60" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="60" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="E7" s="60"/>
       <c r="F7" s="60"/>
@@ -3855,13 +3809,13 @@
         <v>254</v>
       </c>
       <c r="B8" s="60" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="C8" s="60" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="60" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="E8" s="60"/>
       <c r="F8" s="60"/>
@@ -3890,7 +3844,7 @@
         <v>255</v>
       </c>
       <c r="B9" s="60" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="C9" s="60" t="s">
         <v>14</v>
@@ -3956,7 +3910,7 @@
         <v>257</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="C11" s="60" t="s">
         <v>18</v>
@@ -3989,7 +3943,7 @@
         <v>258</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C12" s="60" t="s">
         <v>20</v>
@@ -4022,7 +3976,7 @@
         <v>259</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C13" s="60" t="s">
         <v>22</v>
@@ -4057,7 +4011,7 @@
         <v>261</v>
       </c>
       <c r="B14" s="60" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="C14" s="60" t="s">
         <v>24</v>
@@ -4090,7 +4044,7 @@
         <v>262</v>
       </c>
       <c r="B15" s="60" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="C15" s="60" t="s">
         <v>26</v>
@@ -4123,7 +4077,7 @@
         <v>263</v>
       </c>
       <c r="B16" s="60" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="C16" s="60" t="s">
         <v>28</v>
@@ -4156,7 +4110,7 @@
         <v>264</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>160</v>
+        <v>391</v>
       </c>
       <c r="C17" s="60" t="s">
         <v>30</v>
@@ -4222,7 +4176,7 @@
         <v>268</v>
       </c>
       <c r="B19" s="60" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="C19" s="60" t="s">
         <v>47</v>
@@ -4253,7 +4207,7 @@
         <v>269</v>
       </c>
       <c r="B20" s="60" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="C20" s="60" t="s">
         <v>49</v>
@@ -4284,7 +4238,7 @@
         <v>270</v>
       </c>
       <c r="B21" s="60" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="C21" s="60" t="s">
         <v>271</v>
@@ -4310,18 +4264,18 @@
       </c>
       <c r="M21" s="60"/>
     </row>
-    <row r="22" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A22" s="61" t="s">
         <v>273</v>
       </c>
       <c r="B22" s="60" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="C22" s="60" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D22" s="60" t="s">
-        <v>54</v>
+        <v>274</v>
       </c>
       <c r="E22" s="60"/>
       <c r="F22" s="60"/>
@@ -4337,22 +4291,22 @@
         <v>243</v>
       </c>
       <c r="L22" s="60">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M22" s="60"/>
     </row>
     <row r="23" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A23" s="61" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B23" s="60" t="s">
-        <v>55</v>
+        <v>394</v>
       </c>
       <c r="C23" s="60" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D23" s="60" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E23" s="60"/>
       <c r="F23" s="60"/>
@@ -4368,22 +4322,22 @@
         <v>243</v>
       </c>
       <c r="L23" s="60">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M23" s="60"/>
     </row>
-    <row r="24" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A24" s="61" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B24" s="60" t="s">
-        <v>55</v>
+        <v>394</v>
       </c>
       <c r="C24" s="60" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D24" s="60" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E24" s="60"/>
       <c r="F24" s="60"/>
@@ -4399,22 +4353,22 @@
         <v>243</v>
       </c>
       <c r="L24" s="60">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M24" s="60"/>
     </row>
-    <row r="25" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A25" s="61" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B25" s="60" t="s">
-        <v>55</v>
+        <v>394</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D25" s="60" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E25" s="60"/>
       <c r="F25" s="60"/>
@@ -4430,22 +4384,22 @@
         <v>243</v>
       </c>
       <c r="L25" s="60">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M25" s="60"/>
     </row>
-    <row r="26" spans="1:13" ht="216" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="108" x14ac:dyDescent="0.25">
       <c r="A26" s="61" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B26" s="60" t="s">
-        <v>55</v>
+        <v>394</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E26" s="60"/>
       <c r="F26" s="60"/>
@@ -4461,22 +4415,22 @@
         <v>243</v>
       </c>
       <c r="L26" s="60">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M26" s="60"/>
     </row>
-    <row r="27" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A27" s="61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B27" s="60" t="s">
-        <v>55</v>
+        <v>394</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D27" s="60" t="s">
-        <v>65</v>
+        <v>283</v>
       </c>
       <c r="E27" s="60"/>
       <c r="F27" s="60"/>
@@ -4492,22 +4446,22 @@
         <v>243</v>
       </c>
       <c r="L27" s="60">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M27" s="60"/>
     </row>
-    <row r="28" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A28" s="61" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B28" s="60" t="s">
-        <v>55</v>
+        <v>393</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>66</v>
+        <v>285</v>
       </c>
       <c r="D28" s="60" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E28" s="60"/>
       <c r="F28" s="60"/>
@@ -4523,22 +4477,24 @@
         <v>243</v>
       </c>
       <c r="L28" s="60">
-        <v>51</v>
-      </c>
-      <c r="M28" s="60"/>
-    </row>
-    <row r="29" spans="1:13" ht="108" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="M28" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A29" s="61" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B29" s="60" t="s">
-        <v>55</v>
+        <v>393</v>
       </c>
       <c r="C29" s="60" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D29" s="60" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E29" s="60"/>
       <c r="F29" s="60"/>
@@ -4554,22 +4510,24 @@
         <v>243</v>
       </c>
       <c r="L29" s="60">
-        <v>52</v>
-      </c>
-      <c r="M29" s="60"/>
-    </row>
-    <row r="30" spans="1:13" ht="67.5" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="M29" s="60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A30" s="61" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B30" s="60" t="s">
-        <v>55</v>
+        <v>393</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D30" s="60" t="s">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="E30" s="60"/>
       <c r="F30" s="60"/>
@@ -4585,22 +4543,24 @@
         <v>243</v>
       </c>
       <c r="L30" s="60">
-        <v>53</v>
-      </c>
-      <c r="M30" s="60"/>
-    </row>
-    <row r="31" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="M30" s="60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A31" s="61" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B31" s="60" t="s">
-        <v>55</v>
+        <v>393</v>
       </c>
       <c r="C31" s="60" t="s">
-        <v>72</v>
+        <v>291</v>
       </c>
       <c r="D31" s="60" t="s">
-        <v>289</v>
+        <v>84</v>
       </c>
       <c r="E31" s="60"/>
       <c r="F31" s="60"/>
@@ -4616,22 +4576,24 @@
         <v>243</v>
       </c>
       <c r="L31" s="60">
-        <v>54</v>
-      </c>
-      <c r="M31" s="60"/>
-    </row>
-    <row r="32" spans="1:13" ht="67.5" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="M31" s="60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A32" s="61" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B32" s="60" t="s">
-        <v>55</v>
+        <v>393</v>
       </c>
       <c r="C32" s="60" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="D32" s="60" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E32" s="60"/>
       <c r="F32" s="60"/>
@@ -4647,22 +4609,24 @@
         <v>243</v>
       </c>
       <c r="L32" s="60">
-        <v>55</v>
-      </c>
-      <c r="M32" s="60"/>
-    </row>
-    <row r="33" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="M32" s="60">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A33" s="61" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C33" s="60" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D33" s="60" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E33" s="60"/>
       <c r="F33" s="60"/>
@@ -4678,24 +4642,24 @@
         <v>243</v>
       </c>
       <c r="L33" s="60">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="M33" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A34" s="61" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B34" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C34" s="60" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D34" s="60" t="s">
-        <v>296</v>
+        <v>98</v>
       </c>
       <c r="E34" s="60"/>
       <c r="F34" s="60"/>
@@ -4711,24 +4675,24 @@
         <v>243</v>
       </c>
       <c r="L34" s="60">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="M34" s="60">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A35" s="61" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B35" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C35" s="60" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D35" s="60" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E35" s="60"/>
       <c r="F35" s="60"/>
@@ -4744,24 +4708,24 @@
         <v>243</v>
       </c>
       <c r="L35" s="60">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="M35" s="60">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A36" s="61" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B36" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>299</v>
+        <v>101</v>
       </c>
       <c r="D36" s="60" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="E36" s="60"/>
       <c r="F36" s="60"/>
@@ -4777,24 +4741,24 @@
         <v>243</v>
       </c>
       <c r="L36" s="60">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="M36" s="60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A37" s="61" t="s">
         <v>300</v>
       </c>
       <c r="B37" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C37" s="60" t="s">
         <v>301</v>
       </c>
       <c r="D37" s="60" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="E37" s="60"/>
       <c r="F37" s="60"/>
@@ -4810,21 +4774,21 @@
         <v>243</v>
       </c>
       <c r="L37" s="60">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="M37" s="60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A38" s="61" t="s">
         <v>302</v>
       </c>
       <c r="B38" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C38" s="60" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D38" s="60" t="s">
         <v>303</v>
@@ -4843,24 +4807,24 @@
         <v>243</v>
       </c>
       <c r="L38" s="60">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="M38" s="60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A39" s="61" t="s">
         <v>304</v>
       </c>
       <c r="B39" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C39" s="60" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D39" s="60" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="E39" s="60"/>
       <c r="F39" s="60"/>
@@ -4876,10 +4840,10 @@
         <v>243</v>
       </c>
       <c r="L39" s="60">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="M39" s="60">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="27" x14ac:dyDescent="0.25">
@@ -4887,13 +4851,13 @@
         <v>305</v>
       </c>
       <c r="B40" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C40" s="60" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="D40" s="60" t="s">
-        <v>306</v>
+        <v>112</v>
       </c>
       <c r="E40" s="60"/>
       <c r="F40" s="60"/>
@@ -4909,24 +4873,24 @@
         <v>243</v>
       </c>
       <c r="L40" s="60">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="M40" s="60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A41" s="61" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B41" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C41" s="60" t="s">
-        <v>308</v>
+        <v>117</v>
       </c>
       <c r="D41" s="60" t="s">
-        <v>309</v>
+        <v>118</v>
       </c>
       <c r="E41" s="60"/>
       <c r="F41" s="60"/>
@@ -4942,23 +4906,25 @@
         <v>243</v>
       </c>
       <c r="L41" s="60">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="M41" s="60">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A42" s="61" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B42" s="60" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="C42" s="60" t="s">
-        <v>311</v>
-      </c>
-      <c r="D42" s="60"/>
+        <v>119</v>
+      </c>
+      <c r="D42" s="60" t="s">
+        <v>120</v>
+      </c>
       <c r="E42" s="60"/>
       <c r="F42" s="60"/>
       <c r="G42" s="60"/>
@@ -4966,32 +4932,32 @@
         <v>240</v>
       </c>
       <c r="I42" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J42" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J42" s="62"/>
       <c r="K42" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L42" s="60">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="M42" s="60">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A43" s="61" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B43" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C43" s="60" t="s">
-        <v>313</v>
-      </c>
-      <c r="D43" s="60"/>
+        <v>122</v>
+      </c>
+      <c r="D43" s="60" t="s">
+        <v>123</v>
+      </c>
       <c r="E43" s="60"/>
       <c r="F43" s="60"/>
       <c r="G43" s="60"/>
@@ -4999,33 +4965,31 @@
         <v>240</v>
       </c>
       <c r="I43" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="J43" s="62" t="s">
-        <v>248</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="J43" s="62"/>
       <c r="K43" s="60" t="s">
         <v>243</v>
       </c>
       <c r="L43" s="60">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M43" s="60">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A44" s="61" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B44" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C44" s="60" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="D44" s="60" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="E44" s="60"/>
       <c r="F44" s="60"/>
@@ -5041,24 +5005,24 @@
         <v>243</v>
       </c>
       <c r="L44" s="60">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="M44" s="60">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A45" s="61" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B45" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C45" s="60" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="D45" s="60" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="E45" s="60"/>
       <c r="F45" s="60"/>
@@ -5074,24 +5038,24 @@
         <v>243</v>
       </c>
       <c r="L45" s="60">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="M45" s="60">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="61" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B46" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C46" s="60" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="D46" s="60" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="E46" s="60"/>
       <c r="F46" s="60"/>
@@ -5107,24 +5071,24 @@
         <v>243</v>
       </c>
       <c r="L46" s="60">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="M46" s="60">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A47" s="61" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B47" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C47" s="60" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D47" s="60" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="E47" s="60"/>
       <c r="F47" s="60"/>
@@ -5140,24 +5104,24 @@
         <v>243</v>
       </c>
       <c r="L47" s="60">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="M47" s="60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A48" s="61" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B48" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C48" s="60" t="s">
-        <v>319</v>
+        <v>132</v>
       </c>
       <c r="D48" s="60" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="E48" s="60"/>
       <c r="F48" s="60"/>
@@ -5173,24 +5137,24 @@
         <v>243</v>
       </c>
       <c r="L48" s="60">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="M48" s="60">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A49" s="61" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B49" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C49" s="60" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="D49" s="60" t="s">
-        <v>321</v>
+        <v>135</v>
       </c>
       <c r="E49" s="60"/>
       <c r="F49" s="60"/>
@@ -5206,24 +5170,24 @@
         <v>243</v>
       </c>
       <c r="L49" s="60">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M49" s="60">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A50" s="61" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B50" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C50" s="60" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D50" s="60" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="E50" s="60"/>
       <c r="F50" s="60"/>
@@ -5239,24 +5203,24 @@
         <v>243</v>
       </c>
       <c r="L50" s="60">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="M50" s="60">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="162" x14ac:dyDescent="0.25">
       <c r="A51" s="61" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B51" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C51" s="60" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="D51" s="60" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="E51" s="60"/>
       <c r="F51" s="60"/>
@@ -5272,24 +5236,24 @@
         <v>243</v>
       </c>
       <c r="L51" s="60">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="M51" s="60">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A52" s="61" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B52" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C52" s="60" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D52" s="60" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="E52" s="60"/>
       <c r="F52" s="60"/>
@@ -5305,24 +5269,24 @@
         <v>243</v>
       </c>
       <c r="L52" s="60">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="M52" s="60">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A53" s="61" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B53" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C53" s="60" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="D53" s="60" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E53" s="60"/>
       <c r="F53" s="60"/>
@@ -5338,24 +5302,24 @@
         <v>243</v>
       </c>
       <c r="L53" s="60">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="M53" s="60">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="94.5" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A54" s="61" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B54" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C54" s="60" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="D54" s="60" t="s">
-        <v>118</v>
+        <v>320</v>
       </c>
       <c r="E54" s="60"/>
       <c r="F54" s="60"/>
@@ -5371,24 +5335,24 @@
         <v>243</v>
       </c>
       <c r="L54" s="60">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="M54" s="60">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A55" s="61" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B55" s="60" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C55" s="60" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="D55" s="60" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="E55" s="60"/>
       <c r="F55" s="60"/>
@@ -5404,24 +5368,24 @@
         <v>243</v>
       </c>
       <c r="L55" s="60">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="M55" s="60">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A56" s="61" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B56" s="60" t="s">
-        <v>121</v>
+        <v>390</v>
       </c>
       <c r="C56" s="60" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="D56" s="60" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="E56" s="60"/>
       <c r="F56" s="60"/>
@@ -5437,24 +5401,24 @@
         <v>243</v>
       </c>
       <c r="L56" s="60">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="M56" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="216" x14ac:dyDescent="0.25">
       <c r="A57" s="61" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B57" s="60" t="s">
-        <v>121</v>
+        <v>390</v>
       </c>
       <c r="C57" s="60" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="D57" s="60" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="E57" s="60"/>
       <c r="F57" s="60"/>
@@ -5470,24 +5434,24 @@
         <v>243</v>
       </c>
       <c r="L57" s="60">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="M57" s="60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A58" s="61" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B58" s="60" t="s">
-        <v>121</v>
+        <v>390</v>
       </c>
       <c r="C58" s="60" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="D58" s="60" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="E58" s="60"/>
       <c r="F58" s="60"/>
@@ -5503,24 +5467,24 @@
         <v>243</v>
       </c>
       <c r="L58" s="60">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="M58" s="60">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="61" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B59" s="60" t="s">
-        <v>121</v>
+        <v>390</v>
       </c>
       <c r="C59" s="60" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D59" s="60" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="E59" s="60"/>
       <c r="F59" s="60"/>
@@ -5536,24 +5500,24 @@
         <v>243</v>
       </c>
       <c r="L59" s="60">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="M59" s="60">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A60" s="61" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B60" s="60" t="s">
-        <v>121</v>
+        <v>390</v>
       </c>
       <c r="C60" s="60" t="s">
-        <v>130</v>
+        <v>327</v>
       </c>
       <c r="D60" s="60" t="s">
-        <v>131</v>
+        <v>328</v>
       </c>
       <c r="E60" s="60"/>
       <c r="F60" s="60"/>
@@ -5569,24 +5533,24 @@
         <v>243</v>
       </c>
       <c r="L60" s="60">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="M60" s="60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A61" s="61" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B61" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C61" s="60" t="s">
-        <v>132</v>
+        <v>330</v>
       </c>
       <c r="D61" s="60" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="E61" s="60"/>
       <c r="F61" s="60"/>
@@ -5602,24 +5566,24 @@
         <v>243</v>
       </c>
       <c r="L61" s="60">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="M61" s="60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A62" s="61" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B62" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C62" s="60" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="D62" s="60" t="s">
-        <v>135</v>
+        <v>332</v>
       </c>
       <c r="E62" s="60"/>
       <c r="F62" s="60"/>
@@ -5635,24 +5599,24 @@
         <v>243</v>
       </c>
       <c r="L62" s="60">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="M62" s="60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A63" s="61" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B63" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C63" s="60" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="D63" s="60" t="s">
-        <v>137</v>
+        <v>392</v>
       </c>
       <c r="E63" s="60"/>
       <c r="F63" s="60"/>
@@ -5668,24 +5632,24 @@
         <v>243</v>
       </c>
       <c r="L63" s="60">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="M63" s="60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="162" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A64" s="61" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B64" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C64" s="60" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="D64" s="60" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="E64" s="60"/>
       <c r="F64" s="60"/>
@@ -5701,24 +5665,24 @@
         <v>243</v>
       </c>
       <c r="L64" s="60">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="M64" s="60">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A65" s="61" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B65" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C65" s="60" t="s">
-        <v>338</v>
+        <v>169</v>
       </c>
       <c r="D65" s="60" t="s">
-        <v>141</v>
+        <v>336</v>
       </c>
       <c r="E65" s="60"/>
       <c r="F65" s="60"/>
@@ -5734,24 +5698,24 @@
         <v>243</v>
       </c>
       <c r="L65" s="60">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="M65" s="60">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A66" s="61" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B66" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C66" s="60" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="D66" s="60" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="E66" s="60"/>
       <c r="F66" s="60"/>
@@ -5767,24 +5731,24 @@
         <v>243</v>
       </c>
       <c r="L66" s="60">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="M66" s="60">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A67" s="61" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B67" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C67" s="60" t="s">
-        <v>144</v>
+        <v>339</v>
       </c>
       <c r="D67" s="60" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="E67" s="60"/>
       <c r="F67" s="60"/>
@@ -5800,24 +5764,24 @@
         <v>243</v>
       </c>
       <c r="L67" s="60">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="M67" s="60">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A68" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="B68" s="60" t="s">
+        <v>391</v>
+      </c>
+      <c r="C68" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="D68" s="60" t="s">
         <v>341</v>
-      </c>
-      <c r="B68" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="C68" s="60" t="s">
-        <v>146</v>
-      </c>
-      <c r="D68" s="60" t="s">
-        <v>342</v>
       </c>
       <c r="E68" s="60"/>
       <c r="F68" s="60"/>
@@ -5833,24 +5797,24 @@
         <v>243</v>
       </c>
       <c r="L68" s="60">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="M68" s="60">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A69" s="61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B69" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C69" s="60" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="D69" s="60" t="s">
-        <v>149</v>
+        <v>178</v>
       </c>
       <c r="E69" s="60"/>
       <c r="F69" s="60"/>
@@ -5866,24 +5830,24 @@
         <v>243</v>
       </c>
       <c r="L69" s="60">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="M69" s="60">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A70" s="61" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B70" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C70" s="60" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="D70" s="60" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="E70" s="60"/>
       <c r="F70" s="60"/>
@@ -5899,24 +5863,24 @@
         <v>243</v>
       </c>
       <c r="L70" s="60">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="M70" s="60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="216" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A71" s="61" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B71" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C71" s="60" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="D71" s="60" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="E71" s="60"/>
       <c r="F71" s="60"/>
@@ -5932,24 +5896,24 @@
         <v>243</v>
       </c>
       <c r="L71" s="60">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="M71" s="60">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A72" s="61" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B72" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C72" s="60" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="D72" s="60" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="E72" s="60"/>
       <c r="F72" s="60"/>
@@ -5965,24 +5929,24 @@
         <v>243</v>
       </c>
       <c r="L72" s="60">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="M72" s="60">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A73" s="61" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B73" s="60" t="s">
-        <v>121</v>
+        <v>391</v>
       </c>
       <c r="C73" s="60" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="D73" s="60" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="E73" s="60"/>
       <c r="F73" s="60"/>
@@ -5998,18 +5962,18 @@
         <v>243</v>
       </c>
       <c r="L73" s="60">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="M73" s="60">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A74" s="61" t="s">
+        <v>347</v>
+      </c>
+      <c r="B74" s="60" t="s">
         <v>348</v>
-      </c>
-      <c r="B74" s="60" t="s">
-        <v>121</v>
       </c>
       <c r="C74" s="60" t="s">
         <v>349</v>
@@ -6028,27 +5992,27 @@
       </c>
       <c r="J74" s="62"/>
       <c r="K74" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L74" s="60">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="M74" s="60">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A75" s="61" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B75" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C75" s="60" t="s">
-        <v>352</v>
+        <v>194</v>
       </c>
       <c r="D75" s="60" t="s">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="E75" s="60"/>
       <c r="F75" s="60"/>
@@ -6061,27 +6025,25 @@
       </c>
       <c r="J75" s="62"/>
       <c r="K75" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L75" s="60">
-        <v>106</v>
-      </c>
-      <c r="M75" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="M75" s="60"/>
+    </row>
+    <row r="76" spans="1:13" ht="54" x14ac:dyDescent="0.25">
       <c r="A76" s="61" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B76" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C76" s="60" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="D76" s="60" t="s">
-        <v>354</v>
+        <v>197</v>
       </c>
       <c r="E76" s="60"/>
       <c r="F76" s="60"/>
@@ -6094,10 +6056,10 @@
       </c>
       <c r="J76" s="62"/>
       <c r="K76" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L76" s="60">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="M76" s="60">
         <v>2</v>
@@ -6108,13 +6070,13 @@
         <v>355</v>
       </c>
       <c r="B77" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C77" s="60" t="s">
-        <v>165</v>
+        <v>356</v>
       </c>
       <c r="D77" s="60" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="E77" s="60"/>
       <c r="F77" s="60"/>
@@ -6127,10 +6089,10 @@
       </c>
       <c r="J77" s="62"/>
       <c r="K77" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L77" s="60">
-        <v>108</v>
+        <v>5</v>
       </c>
       <c r="M77" s="60">
         <v>3</v>
@@ -6138,16 +6100,16 @@
     </row>
     <row r="78" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A78" s="61" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B78" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C78" s="60" t="s">
-        <v>167</v>
+        <v>358</v>
       </c>
       <c r="D78" s="60" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="E78" s="60"/>
       <c r="F78" s="60"/>
@@ -6160,27 +6122,27 @@
       </c>
       <c r="J78" s="62"/>
       <c r="K78" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L78" s="60">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="M78" s="60">
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="54" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A79" s="61" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B79" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C79" s="60" t="s">
-        <v>169</v>
+        <v>360</v>
       </c>
       <c r="D79" s="60" t="s">
-        <v>358</v>
+        <v>202</v>
       </c>
       <c r="E79" s="60"/>
       <c r="F79" s="60"/>
@@ -6193,10 +6155,10 @@
       </c>
       <c r="J79" s="62"/>
       <c r="K79" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L79" s="60">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="M79" s="60">
         <v>5</v>
@@ -6204,16 +6166,16 @@
     </row>
     <row r="80" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A80" s="61" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B80" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C80" s="60" t="s">
-        <v>171</v>
+        <v>362</v>
       </c>
       <c r="D80" s="60" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E80" s="60"/>
       <c r="F80" s="60"/>
@@ -6226,10 +6188,10 @@
       </c>
       <c r="J80" s="62"/>
       <c r="K80" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L80" s="60">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="M80" s="60">
         <v>6</v>
@@ -6237,16 +6199,16 @@
     </row>
     <row r="81" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A81" s="61" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B81" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C81" s="60" t="s">
-        <v>361</v>
+        <v>205</v>
       </c>
       <c r="D81" s="60" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="E81" s="60"/>
       <c r="F81" s="60"/>
@@ -6259,10 +6221,10 @@
       </c>
       <c r="J81" s="62"/>
       <c r="K81" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L81" s="60">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="M81" s="60">
         <v>7</v>
@@ -6270,16 +6232,16 @@
     </row>
     <row r="82" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A82" s="61" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B82" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C82" s="60" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="D82" s="60" t="s">
-        <v>363</v>
+        <v>208</v>
       </c>
       <c r="E82" s="60"/>
       <c r="F82" s="60"/>
@@ -6292,27 +6254,27 @@
       </c>
       <c r="J82" s="62"/>
       <c r="K82" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L82" s="60">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="M82" s="60">
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A83" s="61" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B83" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C83" s="60" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="D83" s="60" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="E83" s="60"/>
       <c r="F83" s="60"/>
@@ -6325,27 +6287,27 @@
       </c>
       <c r="J83" s="62"/>
       <c r="K83" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L83" s="60">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="M83" s="60">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A84" s="61" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B84" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C84" s="60" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D84" s="60" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="E84" s="60"/>
       <c r="F84" s="60"/>
@@ -6358,27 +6320,27 @@
       </c>
       <c r="J84" s="62"/>
       <c r="K84" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L84" s="60">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="M84" s="60">
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A85" s="61" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B85" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C85" s="60" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="D85" s="60" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="E85" s="60"/>
       <c r="F85" s="60"/>
@@ -6391,27 +6353,27 @@
       </c>
       <c r="J85" s="62"/>
       <c r="K85" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L85" s="60">
-        <v>116</v>
+        <v>13</v>
       </c>
       <c r="M85" s="60">
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="27" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A86" s="61" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B86" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C86" s="60" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D86" s="60" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="E86" s="60"/>
       <c r="F86" s="60"/>
@@ -6424,27 +6386,27 @@
       </c>
       <c r="J86" s="62"/>
       <c r="K86" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L86" s="60">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="M86" s="60">
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A87" s="61" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B87" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C87" s="60" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="D87" s="60" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="E87" s="60"/>
       <c r="F87" s="60"/>
@@ -6457,27 +6419,27 @@
       </c>
       <c r="J87" s="62"/>
       <c r="K87" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L87" s="60">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="M87" s="60">
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A88" s="61" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B88" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C88" s="60" t="s">
-        <v>370</v>
+        <v>217</v>
       </c>
       <c r="D88" s="60" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="E88" s="60"/>
       <c r="F88" s="60"/>
@@ -6490,27 +6452,27 @@
       </c>
       <c r="J88" s="62"/>
       <c r="K88" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L88" s="60">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="M88" s="60">
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A89" s="61" t="s">
         <v>371</v>
       </c>
       <c r="B89" s="60" t="s">
-        <v>160</v>
+        <v>348</v>
       </c>
       <c r="C89" s="60" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="D89" s="60" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="E89" s="60"/>
       <c r="F89" s="60"/>
@@ -6523,27 +6485,27 @@
       </c>
       <c r="J89" s="62"/>
       <c r="K89" s="60" t="s">
-        <v>243</v>
+        <v>351</v>
       </c>
       <c r="L89" s="60">
-        <v>120</v>
-      </c>
-      <c r="M89" s="60" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="M89" s="60">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A90" s="61" t="s">
         <v>372</v>
       </c>
       <c r="B90" s="60" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="C90" s="60" t="s">
-        <v>374</v>
+        <v>221</v>
       </c>
       <c r="D90" s="60" t="s">
-        <v>375</v>
+        <v>222</v>
       </c>
       <c r="E90" s="60"/>
       <c r="F90" s="60"/>
@@ -6556,27 +6518,27 @@
       </c>
       <c r="J90" s="62"/>
       <c r="K90" s="60" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="L90" s="60">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M90" s="60">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:13" ht="27" x14ac:dyDescent="0.25">
       <c r="A91" s="61" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B91" s="60" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
       <c r="C91" s="60" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="D91" s="60" t="s">
-        <v>378</v>
+        <v>224</v>
       </c>
       <c r="E91" s="60"/>
       <c r="F91" s="60"/>
@@ -6589,547 +6551,21 @@
       </c>
       <c r="J91" s="62"/>
       <c r="K91" s="60" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="L91" s="60">
-        <v>3</v>
-      </c>
-      <c r="M91" s="60"/>
-    </row>
-    <row r="92" spans="1:13" ht="54" x14ac:dyDescent="0.25">
-      <c r="A92" s="61" t="s">
-        <v>379</v>
-      </c>
-      <c r="B92" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C92" s="60" t="s">
-        <v>196</v>
-      </c>
-      <c r="D92" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="E92" s="60"/>
-      <c r="F92" s="60"/>
-      <c r="G92" s="60"/>
-      <c r="H92" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I92" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J92" s="62"/>
-      <c r="K92" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L92" s="60">
-        <v>4</v>
-      </c>
-      <c r="M92" s="60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A93" s="61" t="s">
-        <v>380</v>
-      </c>
-      <c r="B93" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C93" s="60" t="s">
-        <v>381</v>
-      </c>
-      <c r="D93" s="60" t="s">
-        <v>199</v>
-      </c>
-      <c r="E93" s="60"/>
-      <c r="F93" s="60"/>
-      <c r="G93" s="60"/>
-      <c r="H93" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I93" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J93" s="62"/>
-      <c r="K93" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L93" s="60">
-        <v>5</v>
-      </c>
-      <c r="M93" s="60">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A94" s="61" t="s">
-        <v>382</v>
-      </c>
-      <c r="B94" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C94" s="60" t="s">
-        <v>383</v>
-      </c>
-      <c r="D94" s="60" t="s">
-        <v>199</v>
-      </c>
-      <c r="E94" s="60"/>
-      <c r="F94" s="60"/>
-      <c r="G94" s="60"/>
-      <c r="H94" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I94" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J94" s="62"/>
-      <c r="K94" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L94" s="60">
-        <v>6</v>
-      </c>
-      <c r="M94" s="60">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A95" s="61" t="s">
-        <v>384</v>
-      </c>
-      <c r="B95" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C95" s="60" t="s">
-        <v>385</v>
-      </c>
-      <c r="D95" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="E95" s="60"/>
-      <c r="F95" s="60"/>
-      <c r="G95" s="60"/>
-      <c r="H95" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I95" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J95" s="62"/>
-      <c r="K95" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L95" s="60">
-        <v>7</v>
-      </c>
-      <c r="M95" s="60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A96" s="61" t="s">
-        <v>386</v>
-      </c>
-      <c r="B96" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C96" s="60" t="s">
-        <v>387</v>
-      </c>
-      <c r="D96" s="60" t="s">
-        <v>204</v>
-      </c>
-      <c r="E96" s="60"/>
-      <c r="F96" s="60"/>
-      <c r="G96" s="60"/>
-      <c r="H96" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I96" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J96" s="62"/>
-      <c r="K96" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L96" s="60">
-        <v>8</v>
-      </c>
-      <c r="M96" s="60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A97" s="61" t="s">
-        <v>388</v>
-      </c>
-      <c r="B97" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C97" s="60" t="s">
-        <v>205</v>
-      </c>
-      <c r="D97" s="60" t="s">
-        <v>206</v>
-      </c>
-      <c r="E97" s="60"/>
-      <c r="F97" s="60"/>
-      <c r="G97" s="60"/>
-      <c r="H97" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I97" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J97" s="62"/>
-      <c r="K97" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L97" s="60">
-        <v>9</v>
-      </c>
-      <c r="M97" s="60">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A98" s="61" t="s">
-        <v>389</v>
-      </c>
-      <c r="B98" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C98" s="60" t="s">
-        <v>207</v>
-      </c>
-      <c r="D98" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="E98" s="60"/>
-      <c r="F98" s="60"/>
-      <c r="G98" s="60"/>
-      <c r="H98" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I98" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J98" s="62"/>
-      <c r="K98" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L98" s="60">
-        <v>10</v>
-      </c>
-      <c r="M98" s="60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A99" s="61" t="s">
-        <v>390</v>
-      </c>
-      <c r="B99" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C99" s="60" t="s">
-        <v>209</v>
-      </c>
-      <c r="D99" s="60" t="s">
-        <v>210</v>
-      </c>
-      <c r="E99" s="60"/>
-      <c r="F99" s="60"/>
-      <c r="G99" s="60"/>
-      <c r="H99" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I99" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J99" s="62"/>
-      <c r="K99" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L99" s="60">
-        <v>11</v>
-      </c>
-      <c r="M99" s="60">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A100" s="61" t="s">
-        <v>391</v>
-      </c>
-      <c r="B100" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C100" s="60" t="s">
-        <v>211</v>
-      </c>
-      <c r="D100" s="60" t="s">
-        <v>212</v>
-      </c>
-      <c r="E100" s="60"/>
-      <c r="F100" s="60"/>
-      <c r="G100" s="60"/>
-      <c r="H100" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I100" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J100" s="62"/>
-      <c r="K100" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L100" s="60">
-        <v>12</v>
-      </c>
-      <c r="M100" s="60">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A101" s="61" t="s">
-        <v>392</v>
-      </c>
-      <c r="B101" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C101" s="60" t="s">
-        <v>213</v>
-      </c>
-      <c r="D101" s="60" t="s">
-        <v>199</v>
-      </c>
-      <c r="E101" s="60"/>
-      <c r="F101" s="60"/>
-      <c r="G101" s="60"/>
-      <c r="H101" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I101" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J101" s="62"/>
-      <c r="K101" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L101" s="60">
-        <v>13</v>
-      </c>
-      <c r="M101" s="60">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A102" s="61" t="s">
-        <v>393</v>
-      </c>
-      <c r="B102" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C102" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="D102" s="60" t="s">
-        <v>215</v>
-      </c>
-      <c r="E102" s="60"/>
-      <c r="F102" s="60"/>
-      <c r="G102" s="60"/>
-      <c r="H102" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I102" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J102" s="62"/>
-      <c r="K102" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L102" s="60">
-        <v>14</v>
-      </c>
-      <c r="M102" s="60">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="A103" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="B103" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C103" s="60" t="s">
-        <v>216</v>
-      </c>
-      <c r="D103" s="60" t="s">
-        <v>215</v>
-      </c>
-      <c r="E103" s="60"/>
-      <c r="F103" s="60"/>
-      <c r="G103" s="60"/>
-      <c r="H103" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I103" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J103" s="62"/>
-      <c r="K103" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L103" s="60">
-        <v>15</v>
-      </c>
-      <c r="M103" s="60">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A104" s="61" t="s">
-        <v>395</v>
-      </c>
-      <c r="B104" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C104" s="60" t="s">
-        <v>217</v>
-      </c>
-      <c r="D104" s="60" t="s">
-        <v>218</v>
-      </c>
-      <c r="E104" s="60"/>
-      <c r="F104" s="60"/>
-      <c r="G104" s="60"/>
-      <c r="H104" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I104" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J104" s="62"/>
-      <c r="K104" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L104" s="60">
-        <v>16</v>
-      </c>
-      <c r="M104" s="60">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A105" s="61" t="s">
-        <v>396</v>
-      </c>
-      <c r="B105" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C105" s="60" t="s">
-        <v>219</v>
-      </c>
-      <c r="D105" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="E105" s="60"/>
-      <c r="F105" s="60"/>
-      <c r="G105" s="60"/>
-      <c r="H105" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I105" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J105" s="62"/>
-      <c r="K105" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L105" s="60">
-        <v>17</v>
-      </c>
-      <c r="M105" s="60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A106" s="61" t="s">
-        <v>397</v>
-      </c>
-      <c r="B106" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C106" s="60" t="s">
-        <v>221</v>
-      </c>
-      <c r="D106" s="60" t="s">
-        <v>222</v>
-      </c>
-      <c r="E106" s="60"/>
-      <c r="F106" s="60"/>
-      <c r="G106" s="60"/>
-      <c r="H106" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I106" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J106" s="62"/>
-      <c r="K106" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L106" s="60">
-        <v>18</v>
-      </c>
-      <c r="M106" s="60">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" ht="27" x14ac:dyDescent="0.25">
-      <c r="A107" s="61" t="s">
-        <v>398</v>
-      </c>
-      <c r="B107" s="60" t="s">
-        <v>373</v>
-      </c>
-      <c r="C107" s="60" t="s">
-        <v>223</v>
-      </c>
-      <c r="D107" s="60" t="s">
-        <v>224</v>
-      </c>
-      <c r="E107" s="60"/>
-      <c r="F107" s="60"/>
-      <c r="G107" s="60"/>
-      <c r="H107" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I107" s="60" t="s">
-        <v>245</v>
-      </c>
-      <c r="J107" s="62"/>
-      <c r="K107" s="60" t="s">
-        <v>376</v>
-      </c>
-      <c r="L107" s="60">
         <v>19</v>
       </c>
-      <c r="M107" s="60">
+      <c r="M91" s="60">
         <v>16</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="B2:B107" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="B2:B91" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Ерөнхий,Даатгалын хяналтын чиглэлээс,ХЗХХЧ-ээс,ХОҮЭХЧ-ээс,ХЗХГ,МУТА,ВХҮҮ,Сургалт"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2:I107" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="I2:I91" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"draft,needs_answer,needs_review,ready"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7161,19 +6597,19 @@
   <sheetData>
     <row r="1" spans="1:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="58" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="B1" s="58" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="C1" s="58" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="D1" s="58" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="E1" s="58" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="F1" s="58" t="s">
         <v>229</v>
@@ -7185,7 +6621,7 @@
         <v>233</v>
       </c>
       <c r="J1" s="63" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -7198,7 +6634,7 @@
       <c r="G2" s="59"/>
       <c r="H2" s="59"/>
       <c r="J2" s="60" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
